--- a/out/Attention-S4_repeat_1_000008.xlsx
+++ b/out/Attention-S4_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.9470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.9470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3470245394981236</v>
+        <v>-0.5903981995424215</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3470245394981236</v>
+        <v>-0.5903981995424215</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001079152904243674</v>
+        <v>-0.0001570529372650199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1239739416555317</v>
+        <v>-0.1804236601204272</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3470245394981236</v>
+        <v>2.50126221553543</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1805807130576922</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3470245394981236</v>
+        <v>1.901262215535431</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1241771162799991</v>
+        <v>-0.1807019536251748</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3425306140539272</v>
+        <v>0.4359534692671244</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5615422976287657</v>
+        <v>0.6920420315341362</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02440523433501151</v>
+        <v>0.03106159315427013</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2672722545613483</v>
+        <v>0.3175124313599474</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04279846564499575</v>
+        <v>0.05447145105198755</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.328455990665372</v>
+        <v>0.3953833743347307</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05199539308652176</v>
+        <v>0.06617606821431267</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3896439822329162</v>
+        <v>0.4732595008726218</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01375911875246925</v>
+        <v>0.01751184570395345</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3651007726826726</v>
+        <v>0.4420223407608899</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007642825610077076</v>
+        <v>0.009728496174851527</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.366615125808418</v>
+        <v>0.4439510797917934</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0160608767318319</v>
+        <v>0.02044167617043864</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.391102652206206</v>
+        <v>0.4751178767977471</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006305904656302845</v>
+        <v>0.008028051350078062</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3876419101907201</v>
+        <v>0.4707145380884779</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004490180962261729</v>
+        <v>0.005714884908234803</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3903125263288596</v>
+        <v>0.4741146354967845</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00176433223209581</v>
+        <v>0.002246383607685996</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3893475113247721</v>
+        <v>0.4728876986513312</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009984599717231645</v>
+        <v>0.00127283151545085</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3895806104572986</v>
+        <v>0.4731858499181615</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003778443692022413</v>
+        <v>0.0004823632307329145</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3893354943931177</v>
+        <v>0.4728751806953549</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001744565522768361</v>
+        <v>0.0002228988117871476</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3893062908037119</v>
+        <v>0.4728393701247084</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.039334884267193e-05</v>
+        <v>7.896183061281334e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3892532783067887</v>
+        <v>0.4727731019156365</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.455641581801909e-05</v>
+        <v>1.980325908626812e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3892211273894997</v>
+        <v>0.4727336666059042</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.539715033180046e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3892161124966589</v>
+        <v>0.4727286472452113</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.389211876327585</v>
+        <v>0.4727245924523757</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3892088924484793</v>
+        <v>0.4727219750489569</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.389203448703473</v>
+        <v>0.4727164578069672</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3891974559700426</v>
+        <v>0.4727101338129593</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3891920881814642</v>
+        <v>0.4727047660243809</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3891921249299559</v>
+        <v>0.4727048027728726</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3891922351754315</v>
+        <v>0.4727049130183482</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3891923086724151</v>
+        <v>0.4727049865153318</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3891924924148742</v>
+        <v>0.472705170257791</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3891940358515307</v>
+        <v>0.4727067136944474</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3891955057912038</v>
+        <v>0.4727081836341205</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3891967552399258</v>
+        <v>0.4727094330828425</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3891981149341231</v>
+        <v>0.4727107927770398</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3891959100246138</v>
+        <v>0.4727085878675305</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3891955057912038</v>
+        <v>0.4727081836341205</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3891946605758919</v>
+        <v>0.4727073384188085</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3891952118032691</v>
+        <v>0.4727078896461858</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3891948810668427</v>
+        <v>0.4727075589097594</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3891945870789082</v>
+        <v>0.4727072649218249</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3891946605758919</v>
+        <v>0.4727073384188085</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.729251253104851</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3891942195939899</v>
+        <v>0.4727068974369066</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.729251253104851</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3891941093485143</v>
+        <v>0.4727067871914311</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3891940726000226</v>
+        <v>0.4727067504429394</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.729251253104851</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3891942195939899</v>
+        <v>0.4727068974369066</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.729251253104851</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3891937418635962</v>
+        <v>0.4727064197065129</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3891946973243836</v>
+        <v>0.4727073751673002</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3891946605758919</v>
+        <v>0.4727073384188085</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3891943298394654</v>
+        <v>0.4727070076823821</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3891947708213674</v>
+        <v>0.4727074486642841</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3891941460970063</v>
+        <v>0.472706823939923</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3891939623545471</v>
+        <v>0.4727066401974638</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3891935581211371</v>
+        <v>0.4727062359640538</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3891927129058251</v>
+        <v>0.4727053907487418</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3891926761573334</v>
+        <v>0.4727053540002501</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3891928231513007</v>
+        <v>0.4727055009942174</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.389192749654317</v>
+        <v>0.4727054274972337</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3891928231513007</v>
+        <v>0.4727055009942174</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3891928598997926</v>
+        <v>0.4727055377427093</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.389192749654317</v>
+        <v>0.4727054274972337</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.389193190636219</v>
+        <v>0.4727058684791357</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3891930803907435</v>
+        <v>0.4727057582336601</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3891930436422515</v>
+        <v>0.4727057214851682</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3891929701452679</v>
+        <v>0.4727056479881846</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3891929333967762</v>
+        <v>0.4727056112396929</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3891927129058251</v>
+        <v>0.4727053907487418</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3891926394088415</v>
+        <v>0.4727053172517582</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3891925659118579</v>
+        <v>0.4727052437547746</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3891926026603498</v>
+        <v>0.4727052805032665</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3891924924148742</v>
+        <v>0.472705170257791</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3891926026603498</v>
+        <v>0.4727052805032665</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.190398199542422</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3891928966482843</v>
+        <v>0.472705574491201</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000008.xlsx
+++ b/out/Attention-S4_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001079152904243674</v>
+        <v>-0.0001092075234309304</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1239739416555317</v>
+        <v>-0.1254584691838786</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1240818569459561</v>
+        <v>-0.1255676767073095</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1241771162799991</v>
+        <v>-0.1256640239984965</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3425306140539272</v>
+        <v>0.3464429169179528</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5615422976287657</v>
+        <v>0.5678869929241966</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02440523433501151</v>
+        <v>0.02468394850639657</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2672722545613483</v>
+        <v>0.2702563138889689</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04279846564499575</v>
+        <v>0.04328736365749068</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.328455990665372</v>
+        <v>0.3321387818937968</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05199539308652176</v>
+        <v>0.05258903464677227</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3896439822329162</v>
+        <v>0.3940253687142376</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01375911875246925</v>
+        <v>0.01391621118311796</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3651007726826726</v>
+        <v>0.3692019445419495</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007642825610077076</v>
+        <v>0.007730141281918118</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.366615125808418</v>
+        <v>0.3707336442111051</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0160608767318319</v>
+        <v>0.01624424469989176</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.391102652206206</v>
+        <v>0.3955007461285456</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006305904656302845</v>
+        <v>0.006378569073761715</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3876419101907201</v>
+        <v>0.3920005488819666</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004490180962261729</v>
+        <v>0.004540204081181757</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3903125263288596</v>
+        <v>0.3947014541989174</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00176433223209581</v>
+        <v>0.001784700600078494</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3893475113247721</v>
+        <v>0.3937253876023041</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009984599717231645</v>
+        <v>0.00101079127705924</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3895806104572986</v>
+        <v>0.3939612266838008</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003778443692022413</v>
+        <v>0.0003813674768942865</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3893354943931177</v>
+        <v>0.3937135334776696</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001744565522768361</v>
+        <v>0.0001766584731636684</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3893062908037119</v>
+        <v>0.3936840329117065</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.039334884267193e-05</v>
+        <v>6.12006741370259e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3892532783067887</v>
+        <v>0.3936304312973886</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3892211273894997</v>
+        <v>0.3935979496436734</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.539715033180046e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3892161124966589</v>
+        <v>0.3935929340061906</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.389211876327585</v>
+        <v>0.3935886978371166</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3892088924484793</v>
+        <v>0.393585713958011</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.389203448703473</v>
+        <v>0.3935802702130047</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3891974559700426</v>
+        <v>0.3935742774795743</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3891920881814642</v>
+        <v>0.3935689096909959</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3891921249299559</v>
+        <v>0.3935689464394876</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3891922351754315</v>
+        <v>0.3935690566849632</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3891923086724151</v>
+        <v>0.3935691301819468</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3891924924148742</v>
+        <v>0.393569313924406</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3891940358515307</v>
+        <v>0.3935708573610625</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3470245394981236</v>
+        <v>0.4036739699415705</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3891955057912038</v>
+        <v>0.3935723273007355</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3470245394981236</v>
+        <v>-0.4366176397962522</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3891967552399258</v>
+        <v>0.3935735767494575</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.276909249534075</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3891981149341231</v>
+        <v>0.3935749364436548</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3891959100246138</v>
+        <v>0.3935727315341455</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3891955057912038</v>
+        <v>0.3935723273007355</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3891946605758919</v>
+        <v>0.3935714820854235</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3891952118032691</v>
+        <v>0.3935720333128008</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.276909249534075</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3891948810668427</v>
+        <v>0.3935717025763744</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3470245394981236</v>
+        <v>-0.4366176397962522</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3891945870789082</v>
+        <v>0.3935714085884399</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9470245394981236</v>
+        <v>-0.2366176397962522</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3891946605758919</v>
+        <v>0.3935714820854235</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.729251253104851</v>
+        <v>-1.076909249534075</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3891942195939899</v>
+        <v>0.3935710411035216</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.729251253104851</v>
+        <v>-1.076909249534075</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3891941093485143</v>
+        <v>0.3935709308580461</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9470245394981236</v>
+        <v>-1.076909249534075</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3891940726000226</v>
+        <v>0.3935708941095544</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.729251253104851</v>
+        <v>-1.076909249534075</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3891942195939899</v>
+        <v>0.3935710411035216</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.729251253104851</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3891937418635962</v>
+        <v>0.393570563373128</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3891946973243836</v>
+        <v>0.3935715188339152</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3891946605758919</v>
+        <v>0.3935714820854235</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3891943298394654</v>
+        <v>0.3935711513489971</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3891947708213674</v>
+        <v>0.3935715923308991</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3891941460970063</v>
+        <v>0.393570967606538</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3891939623545471</v>
+        <v>0.3935707838640788</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3891935581211371</v>
+        <v>0.3935703796306688</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.076909249534075</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3891927129058251</v>
+        <v>0.3935695344153568</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9470245394981236</v>
+        <v>-0.2366176397962522</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3891926761573334</v>
+        <v>0.3935694976668651</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3891928231513007</v>
+        <v>0.3935696446608324</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.389192749654317</v>
+        <v>0.3935695711638487</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3891928231513007</v>
+        <v>0.3935696446608324</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3891928598997926</v>
+        <v>0.3935696814093243</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.389192749654317</v>
+        <v>0.3935695711638487</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.389193190636219</v>
+        <v>0.3935700121457507</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9470245394981236</v>
+        <v>-0.2366176397962522</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3891930803907435</v>
+        <v>0.3935699019002751</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.276909249534075</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3891930436422515</v>
+        <v>0.3935698651517832</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3891929701452679</v>
+        <v>0.3935697916547996</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-3.32925125310485</v>
+        <v>-2.117200859271897</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3891929333967762</v>
+        <v>0.3935697549063079</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-3.32925125310485</v>
+        <v>-1.276909249534075</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3891927129058251</v>
+        <v>0.3935695344153568</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3470245394981236</v>
+        <v>-0.4366176397962522</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3891926394088415</v>
+        <v>0.3935694609183732</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3891925659118579</v>
+        <v>0.3935693874213896</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3891926026603498</v>
+        <v>0.3935694241698815</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3891924924148742</v>
+        <v>0.393569313924406</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3891926026603498</v>
+        <v>0.3935694241698815</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9470245394981236</v>
+        <v>0.6036739699415705</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3891928966482843</v>
+        <v>0.393569718157816</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000008.xlsx
+++ b/out/Attention-S4_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.008545320481061935</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.009374570101499557</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.04999999999999988</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.009551814757287502</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.00674792192876339</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.005290633998811245</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.005220577120780945</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.004128439351916313</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6036739699415705</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.002441911026835442</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6036739699415705</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.004441604018211365</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.6036739699415705</v>
+        <v>-0.16</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.005471173673868179</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.007273765280842781</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.007046028040349483</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.006036737002432346</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.005765629000961781</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.008101601153612137</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006712836213409901</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.004301868379116058</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.003289544954895973</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.002784330397844315</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0007113739848136902</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002566117793321609</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.00409485399723053</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.003617514856159687</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.00486628245562315</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.005174190737307072</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.005048341117799282</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.005016663111746311</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.003790136426687241</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.003913316875696182</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.007109991274774075</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01001369021832943</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.007388417609035969</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.005667972378432751</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002921988256275654</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001491349190473557</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.004299867898225784</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.00350731797516346</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.003791076131165028</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.006752668879926205</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.006048304028809071</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.006004976108670235</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.00727495551109314</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.008617577143013477</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006425322964787483</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001092075234309304</v>
+        <v>-0.0001100360487170983</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1254584691838786</v>
+        <v>-0.12641028560471</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.00397446658462286</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.005709914490580559</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.00187773909419775</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.00271710567176342</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.00144269410520792</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.001215365715324879</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.002509566023945808</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.003660689108073711</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.003711547702550888</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.002981669269502163</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.002695015631616116</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.00268985889852047</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.004063398577272892</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1255676767073095</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.005003648810088634</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1256640239984965</v>
+        <v>-0.1266142796801953</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3464429169179528</v>
+        <v>0.3378516662002718</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.005284189246594906</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5678869929241966</v>
+        <v>0.5497377402911573</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02468394850639657</v>
+        <v>0.02407186028281137</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.004375006072223186</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2702563138889689</v>
+        <v>0.2594878435008223</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04328736365749068</v>
+        <v>0.04221384114501495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.004474431276321411</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3321387818937968</v>
+        <v>0.3198356321692881</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05258903464677227</v>
+        <v>0.05128451978958311</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.004355387762188911</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3940253687142376</v>
+        <v>0.3801874380827772</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01391621118311796</v>
+        <v>0.01357133389314337</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.001093781553208828</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3692019445419495</v>
+        <v>0.3559794849573241</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007730141281918118</v>
+        <v>0.007538266927410282</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.008155429735779762</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3707336442111051</v>
+        <v>0.3574730659617591</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01624424469989176</v>
+        <v>0.01584052698870113</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.008594118990004063</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3955007461285456</v>
+        <v>0.3816258078128796</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006378569073761715</v>
+        <v>0.006219918428976516</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.007107958197593689</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3920005488819666</v>
+        <v>0.3782121458589583</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004540204081181757</v>
+        <v>0.00442808329739549</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.009407991543412209</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3947014541989174</v>
+        <v>0.3808463147795242</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001784700600078494</v>
+        <v>0.001739890190516589</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01057765074074268</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3937253876023041</v>
+        <v>0.3798941942015497</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00101079127705924</v>
+        <v>0.0009861286663870887</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.0124347023665905</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3939612266838008</v>
+        <v>0.3801241859001874</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003813674768942865</v>
+        <v>0.0003719725230488327</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01205445267260075</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3937135334776696</v>
+        <v>0.3798823851128093</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001766584731636684</v>
+        <v>0.0001722546313900037</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01307751424610615</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3936840329117065</v>
+        <v>0.3798534784999604</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.12006741370259e-05</v>
+        <v>5.958602354831795e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01287014782428741</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3936304312973886</v>
+        <v>0.3798010551204321</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.455641581801909e-05</v>
+        <v>1.407943006636009e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.009256696328520775</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3935979496436734</v>
+        <v>0.3797692356842116</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>4.539715033180046e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.007722588256001472</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.16</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3935929340061906</v>
+        <v>0.3797642207913708</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.009662764146924019</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3935886978371166</v>
+        <v>0.3797599846222969</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.008061898872256279</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.393585713958011</v>
+        <v>0.3797570007431912</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01144093461334705</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3935802702130047</v>
+        <v>0.3797515569981849</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01141914166510105</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3935742774795743</v>
+        <v>0.3797455642647545</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01122125796973705</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3935689096909959</v>
+        <v>0.3797401964761761</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01130400411784649</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3935689464394876</v>
+        <v>0.3797402332246678</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0108452346175909</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3935690566849632</v>
+        <v>0.3797403434701434</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.009956942871212959</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3935691301819468</v>
+        <v>0.379740416967127</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01160418055951595</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4036739699415705</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.393569313924406</v>
+        <v>0.3797406007095862</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.008699053898453712</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3935708573610625</v>
+        <v>0.3797421441462426</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.004979530349373817</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4036739699415705</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3935723273007355</v>
+        <v>0.3797436140859157</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01217002980411053</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4366176397962522</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3935735767494575</v>
+        <v>0.3797448635346377</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.004685023799538612</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.276909249534075</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3935749364436548</v>
+        <v>0.3797462232288351</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01414143852889538</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3935727315341455</v>
+        <v>0.3797440183193257</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.02143924124538898</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3935723273007355</v>
+        <v>0.3797436140859157</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01645484380424023</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3935714820854235</v>
+        <v>0.3797427688706038</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008539440110325813</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3935720333128008</v>
+        <v>0.379743320097981</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.00342162512242794</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.276909249534075</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3935717025763744</v>
+        <v>0.3797429893615546</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.004720715805888176</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4366176397962522</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3935714085884399</v>
+        <v>0.3797426953736202</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01093642599880695</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2366176397962522</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3935714820854235</v>
+        <v>0.3797427688706038</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005695892497897148</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.076909249534075</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3935710411035216</v>
+        <v>0.3797423278887018</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01911077462136745</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.076909249534075</v>
+        <v>0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3935709308580461</v>
+        <v>0.3797422176432262</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.005969533696770668</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.076909249534075</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3935708941095544</v>
+        <v>0.3797421808947345</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01250677742063999</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.076909249534075</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3935710411035216</v>
+        <v>0.3797423278887018</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02578597329556942</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.393570563373128</v>
+        <v>0.3797418501583082</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01410579495131969</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3935715188339152</v>
+        <v>0.3797428056190955</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.03140580654144287</v>
       </c>
       <c r="JB102" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3935714820854235</v>
+        <v>0.3797427688706038</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.0240789707750082</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3935711513489971</v>
+        <v>0.3797424381341774</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01518400199711323</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3935715923308991</v>
+        <v>0.3797428791160793</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01099125109612942</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.393570967606538</v>
+        <v>0.3797422543917182</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003127304837107658</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3935707838640788</v>
+        <v>0.379742070649259</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.007090775296092033</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.117200859271897</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3935703796306688</v>
+        <v>0.379741666415849</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004079481586813927</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.076909249534075</v>
+        <v>0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3935695344153568</v>
+        <v>0.379740821200537</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.002974314615130424</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2366176397962522</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3935694976668651</v>
+        <v>0.3797407844520453</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.008466904982924461</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3935696446608324</v>
+        <v>0.3797409314460126</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.008647868409752846</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3935695711638487</v>
+        <v>0.379740857949029</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.006181297823786736</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3935696446608324</v>
+        <v>0.3797409314460126</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.01177618466317654</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3935696814093243</v>
+        <v>0.3797409681945045</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.007037973031401634</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3935695711638487</v>
+        <v>0.379740857949029</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.004984417930245399</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3935700121457507</v>
+        <v>0.3797412989309309</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.009958267211914062</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2366176397962522</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3935699019002751</v>
+        <v>0.3797411886854554</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001585191115736961</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.276909249534075</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3935698651517832</v>
+        <v>0.3797411519369635</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.00795149989426136</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3935697916547996</v>
+        <v>0.3797410784399798</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002824166789650917</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.117200859271897</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3935697549063079</v>
+        <v>0.3797410416914881</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.000733131542801857</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.276909249534075</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3935695344153568</v>
+        <v>0.379740821200537</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.004564827308058739</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4366176397962522</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3935694609183732</v>
+        <v>0.3797407477035534</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.005337482318282127</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3935693874213896</v>
+        <v>0.3797406742065698</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.007205439731478691</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3935694241698815</v>
+        <v>0.3797407109550617</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.00919884629547596</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.393569313924406</v>
+        <v>0.3797406007095862</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.009284844622015953</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3935694241698815</v>
+        <v>0.3797407109550617</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01134483702480793</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.6036739699415705</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.393569718157816</v>
+        <v>0.3797410049429962</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000008.xlsx
+++ b/out/Attention-S4_repeat_1_000008.xlsx
@@ -83624,7 +83624,7 @@
         <v>-0.01518400199711323</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0.3797428791160793</v>
@@ -84419,7 +84419,7 @@
         <v>-0.01099125109612942</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0.3797422543917182</v>
@@ -85214,7 +85214,7 @@
         <v>-0.003127304837107658</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0.379742070649259</v>
@@ -86009,7 +86009,7 @@
         <v>-0.007090775296092033</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.02000000000000007</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
         <v>0.379741666415849</v>
@@ -86804,7 +86804,7 @@
         <v>-0.004079481586813927</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0.379740821200537</v>
@@ -93164,7 +93164,7 @@
         <v>0.009958267211914062</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
         <v>0.3797411886854554</v>
